--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/ba-uiux-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/ba-uiux-easy.xlsx
@@ -460,19 +460,19 @@
         <v>Wireframe tập trung vào bố cục, phân bổ thông tin (layout). Mockup tập trung vào phần nhìn (visual design) bao gồm màu sắc, font chữ và nhận diện thương hiệu.</v>
       </c>
       <c r="F2" t="str">
+        <v>Wireframe chỉ chạy được trên điện thoại Android; Mockup chỉ chạy được trên iPhone — nền tảng hỗ trợ</v>
+      </c>
+      <c r="G2" t="str">
         <v>Wireframe là bản vẽ khung xương đen trắng cấu trúc trang; Mockup là thiết kế tĩnh có màu sắc, hình ảnh và typography chân thực — cấu trúc vs trực quan</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
+        <v>Wireframe dùng để kiểm thử lỗi bảo mật; Mockup dùng để đo lường tốc độ tải trang — mục đích kỹ thuật</v>
+      </c>
+      <c r="I2" t="str">
         <v>Wireframe do Dev vẽ bằng code; Mockup do khách hàng tự vẽ bằng bút chì trên giấy — chủ thể vẽ</v>
       </c>
-      <c r="H2" t="str">
-        <v>Wireframe chỉ chạy được trên điện thoại Android; Mockup chỉ chạy được trên iPhone — nền tảng hỗ trợ</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Wireframe dùng để kiểm thử lỗi bảo mật; Mockup dùng để đo lường tốc độ tải trang — mục đích kỹ thuật</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>Chuỗi các bước liên tiếp mà người dùng thực hiện trên giao diện để hoàn thành một mục tiêu cụ thể — luồng hành vi giao diện</v>
       </c>
       <c r="G3" t="str">
+        <v>Biểu đồ thể hiện dung lượng bộ nhớ RAM tiêu thụ khi mở một trang web — hiệu năng hệ thống</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Sơ đồ phân quyền các nhóm người dùng trong cơ sở dữ liệu SQL — phân quyền người dùng</v>
+      </c>
+      <c r="I3" t="str">
         <v>Tốc độ di chuyển của chuột máy tính khi người dùng rê qua các nút bấm — tốc độ di trỏ chuột</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Biểu đồ thể hiện dung lượng bộ nhớ RAM tiêu thụ khi mở một trang web — hiệu năng hệ thống</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Sơ đồ phân quyền các nhóm người dùng trong cơ sở dữ liệu SQL — phân quyền người dùng</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -524,19 +524,19 @@
         <v>Định luật Fitts chỉ ra rằng thời gian để đạt được một mục tiêu phụ thuộc vào khoảng cách và kích thước của mục tiêu đó. Nút bấm quan trọng cần thiết kế to và đặt ở vị trí dễ chạm tới.</v>
       </c>
       <c r="F4" t="str">
+        <v>Màu sắc của nút bấm bắt buộc phải là màu đỏ để thu hút sự chú ý của người dùng — quy định màu sắc nút</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Nút bấm phải hiển thị kèm theo âm thanh click khi người dùng nhấn vào — âm thanh phản hồi</v>
+      </c>
+      <c r="H4" t="str">
         <v>Kích thước nút bấm phải đủ lớn và khoảng cách di chuyển chuột đến nút phải đủ ngắn để dễ dàng tương tác — tối ưu hóa thao tác bấm</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Màu sắc của nút bấm bắt buộc phải là màu đỏ để thu hút sự chú ý của người dùng — quy định màu sắc nút</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Nút bấm phải hiển thị kèm theo âm thanh click khi người dùng nhấn vào — âm thanh phản hồi</v>
       </c>
       <c r="I4" t="str">
         <v>Mỗi màn hình chỉ được phép chứa duy nhất một nút bấm duy nhất để tránh nhầm lẫn — giới hạn số nút</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>CTA là nút bấm quan trọng nhất trên màn hình, được thiết kế nổi bật (màu sắc tương phản tốt) nhằm định hướng hành vi của người dùng thực hiện chuyển đổi.</v>
       </c>
       <c r="F5" t="str">
+        <v>Icon hình chiếc điện thoại dùng để khách hàng bấm gọi trực tiếp cho tổng đài — nút gọi điện</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Form nhập thông tin thẻ ngân hàng để thanh toán hóa đơn — form thanh toán</v>
+      </c>
+      <c r="H5" t="str">
         <v>Nút bấm hoặc liên kết nổi bật thúc giục người dùng thực hiện một hành động mục tiêu (như "Đăng ký ngay", "Mua hàng") — phần tử kích hoạt hành động</v>
       </c>
-      <c r="G5" t="str">
+      <c r="I5" t="str">
         <v>Khung hiển thị điều khoản sử dụng dài 10 trang buộc người dùng phải đọc — điều khoản pháp lý</v>
       </c>
-      <c r="H5" t="str">
-        <v>Form nhập thông tin thẻ ngân hàng để thanh toán hóa đơn — form thanh toán</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Icon hình chiếc điện thoại dùng để khách hàng bấm gọi trực tiếp cho tổng đài — nút gọi điện</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Khoảng trắng không phải là khoảng trống vô nghĩa. Nó là công cụ thiết kế giúp nhóm các phần tử liên quan (Proximity), cải thiện độ đọc và giảm tải nhận thức cho người dùng.</v>
       </c>
       <c r="F6" t="str">
-        <v>Giúp giao diện không bị rối mắt, tạo khoảng thở cho các phần tử và làm nổi bật các nội dung quan trọng — tăng tính rõ ràng và tập trung</v>
+        <v>Để tiết kiệm mực in khi BA in tài liệu Wireframe ra giấy cho khách hàng xem — tiết kiệm mực in</v>
       </c>
       <c r="G6" t="str">
         <v>Để giảm thiểu dung lượng file ảnh khi lưu trữ trên máy tính của thiết kế — tiết kiệm bộ nhớ</v>
       </c>
       <c r="H6" t="str">
-        <v>Để tiết kiệm mực in khi BA in tài liệu Wireframe ra giấy cho khách hàng xem — tiết kiệm mực in</v>
+        <v>Vì lập trình viên không biết viết code để lấp đầy các khoảng trống đó — hạn chế kỹ thuật</v>
       </c>
       <c r="I6" t="str">
-        <v>Vì lập trình viên không biết viết code để lấp đầy các khoảng trống đó — hạn chế kỹ thuật</v>
+        <v>Giúp giao diện không bị rối mắt, tạo khoảng thở cho các phần tử và làm nổi bật các nội dung quan trọng — tăng tính rõ ràng và tập trung</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Mobile-First buộc thiết kế tập trung vào những tính năng cốt lõi nhất do giới hạn về không gian màn hình điện thoại, sau đó mới mở rộng dần (Progressive Enhancement) sang màn hình to.</v>
       </c>
       <c r="F7" t="str">
+        <v>Thiết kế giao diện cho đồng hồ thông minh (smartwatch) trước rồi mở rộng ra máy tính — đồng hồ trước</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Thiết kế giao diện chạy trên màn hình tivi thông minh 55 inch trước rồi mới làm di động — tivi trước</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Thiết kế giao diện cho màn hình máy tính bàn trước rồi co nhỏ lại cho điện thoại — máy tính trước</v>
+      </c>
+      <c r="I7" t="str">
         <v>Thiết kế giao diện cho thiết bị di động trước, sau đó mở rộng dần cho máy tính (desktop) — di động trước</v>
       </c>
-      <c r="G7" t="str">
-        <v>Thiết kế giao diện cho màn hình máy tính bàn trước rồi co nhỏ lại cho điện thoại — máy tính trước</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Thiết kế giao diện cho đồng hồ thông minh (smartwatch) trước rồi mở rộng ra máy tính — đồng hồ trước</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Thiết kế giao diện chạy trên màn hình tivi thông minh 55 inch trước rồi mới làm di động — tivi trước</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Breadcrumb (vệt bánh mì) giúp người dùng định vị vị trí hiện tại của mình trong cấu trúc phân cấp website và dễ dàng quay lại các thư mục cha.</v>
       </c>
       <c r="F8" t="str">
-        <v>Thanh điều hướng phân cấp (như Trang chủ &gt; Điện thoại &gt; iPhone) giúp người dùng biết mình đang ở đâu trong hệ thống — định vị phân cấp</v>
+        <v>Khung hiển thị các quảng cáo sản phẩm liên quan ở bên dưới trang chi tiết — khung quảng cáo</v>
       </c>
       <c r="G8" t="str">
-        <v>Khung hiển thị các quảng cáo sản phẩm liên quan ở bên dưới trang chi tiết — khung quảng cáo</v>
+        <v>Thông báo lỗi hệ thống hiển thị dạng popup giữa màn hình — popup báo lỗi</v>
       </c>
       <c r="H8" t="str">
         <v>Icon hình chiếc bánh mì dùng để người dùng bấm đặt đồ ăn trực tuyến — icon đặt đồ ăn</v>
       </c>
       <c r="I8" t="str">
-        <v>Thông báo lỗi hệ thống hiển thị dạng popup giữa màn hình — popup báo lỗi</v>
+        <v>Thanh điều hướng phân cấp (như Trang chủ &gt; Điện thoại &gt; iPhone) giúp người dùng biết mình đang ở đâu trong hệ thống — định vị phân cấp</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -687,13 +687,13 @@
         <v>Đại diện cho vị trí sẽ chèn hình ảnh sau này mà không cần đưa ảnh thật vào làm phân tâm — vị trí chèn ảnh</v>
       </c>
       <c r="G9" t="str">
+        <v>Biểu thị khu vực người dùng không được phép chạm vào trên màn hình — vùng cấm</v>
+      </c>
+      <c r="H9" t="str">
         <v>Biểu thị nút bấm đóng cửa sổ popup hoặc xóa dữ liệu — nút đóng/xóa</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <v>Đánh dấu vùng giao diện đang bị lỗi và cần lập trình viên sửa đổi — vùng lỗi kỹ thuật</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Biểu thị khu vực người dùng không được phép chạm vào trên màn hình — vùng cấm</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -719,13 +719,13 @@
         <v>Các thành phần giao diện tương tự nhau (nút bấm, màu sắc, font chữ) phải hoạt động và hiển thị giống nhau xuyên suốt hệ thống — nhất quán hiển thị hành vi</v>
       </c>
       <c r="G10" t="str">
-        <v>Giao diện phải thay đổi màu sắc liên tục theo thời gian thực để tạo sự thích thú cho người dùng — thay đổi linh hoạt</v>
+        <v>Hệ thống phải bắt buộc người dùng thay đổi mật khẩu sau mỗi 5 phút sử dụng — nhất quán bảo mật</v>
       </c>
       <c r="H10" t="str">
         <v>Mỗi trang web trong hệ thống phải được thiết kế bởi một designer khác nhau để tạo sự đa dạng — đa dạng thiết kế</v>
       </c>
       <c r="I10" t="str">
-        <v>Hệ thống phải bắt buộc người dùng thay đổi mật khẩu sau mỗi 5 phút sử dụng — nhất quán bảo mật</v>
+        <v>Giao diện phải thay đổi màu sắc liên tục theo thời gian thực để tạo sự thích thú cho người dùng — thay đổi linh hoạt</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -751,13 +751,13 @@
         <v>Vì khi người dùng bắt đầu nhập liệu, placeholder sẽ biến mất; nếu không có label phía trên, người dùng dễ quên mất ô đó đang yêu cầu nhập thông tin gì — duy trì thông tin nhãn</v>
       </c>
       <c r="G11" t="str">
+        <v>Để tiết kiệm không gian hiển thị của màn hình điện thoại di động — tiết kiệm diện tích</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Để hệ thống tự động điền thông tin mật khẩu của người dùng vào form — tự động điền</v>
+      </c>
+      <c r="I11" t="str">
         <v>Để lập trình viên dễ viết mã nguồn CSS căn chỉnh lề cho giao diện — dễ code CSS</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Để tiết kiệm không gian hiển thị của màn hình điện thoại di động — tiết kiệm diện tích</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Để hệ thống tự động điền thông tin mật khẩu của người dùng vào form — tự động điền</v>
       </c>
       <c r="J11">
         <v>1</v>
